--- a/fixed_allocation_intraday_intraday.xlsx
+++ b/fixed_allocation_intraday_intraday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,6 +1464,771 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-09-13T06:36:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1308</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-51.5342</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.9943</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1268</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.1308</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-13T06:45:40</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.1391</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-47.9579</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.996</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1351</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1391</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-13T06:54:45</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.1158</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-42.9416</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9892</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.1118</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.1158</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:03:44</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.1477</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-56.0013</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9972</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1438</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.1477</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:12:18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.1291</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-51.8648</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.9938</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.1251</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.1291</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:21:11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.1127</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-45.097</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.9877</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.1086</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.1127</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:29:48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.1193</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-50.6749</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.9907</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1152</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.1195</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:38:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.1536</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-58.6055</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.9978</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.1498</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.1536</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:46:39</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.1403</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-51.4601</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.9962</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.1364</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.1403</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-13T07:55:25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1158</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-44.8604</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.9892</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.1118</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.1159</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:04:04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.1068</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-45.2846</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.9844000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.1027</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.1068</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:12:39</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.1545</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-54.3086</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.9979</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.1506</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.1545</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:21:19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-48.902</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.9945000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.1321</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:30:06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1297</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-52.5448</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.994</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.1257</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.1297</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:38:36</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.1074</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-47.5542</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.9847</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.1033</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.1078</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixed_allocation_intraday_intraday.xlsx
+++ b/fixed_allocation_intraday_intraday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2229,6 +2229,57 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-13T12:17:45</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.1537</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-53.2634</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.9978</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.1498</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.1539</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "allocation", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
